--- a/Excel Files IPEDS/Trimmed/c2010_trimmed_file.xlsx
+++ b/Excel Files IPEDS/Trimmed/c2010_trimmed_file.xlsx
@@ -14,114 +14,117 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
-    <t>UNITID</t>
+    <t>unitid</t>
   </si>
   <si>
-    <t>CIPCODE</t>
+    <t>cipcode</t>
   </si>
   <si>
-    <t>CTOTALT</t>
+    <t>ctotalt</t>
   </si>
   <si>
-    <t>AWLEVEL</t>
+    <t>awlevel</t>
   </si>
   <si>
-    <t>CTOTALM</t>
+    <t>ctotalm</t>
   </si>
   <si>
-    <t>CTOTALW</t>
+    <t>ctotalw</t>
   </si>
   <si>
-    <t>CRACE18</t>
+    <t>crace18</t>
   </si>
   <si>
-    <t>CRACE20</t>
+    <t>crace20</t>
   </si>
   <si>
-    <t>CRACE21</t>
+    <t>crace21</t>
   </si>
   <si>
-    <t>CRACE22</t>
+    <t>crace22</t>
   </si>
   <si>
-    <t>CUNKNT</t>
+    <t>cunknt</t>
   </si>
   <si>
-    <t>CRACE19</t>
+    <t>crace19</t>
   </si>
   <si>
-    <t>CBKAAT</t>
+    <t>cbkaat</t>
   </si>
   <si>
-    <t>CASIAT</t>
+    <t>casiat</t>
   </si>
   <si>
-    <t>CNHPIT</t>
+    <t>cnhpit</t>
   </si>
   <si>
-    <t>CHISPT</t>
+    <t>chispt</t>
   </si>
   <si>
-    <t>CWHITT</t>
+    <t>cwhitt</t>
   </si>
   <si>
-    <t>C2MORT</t>
+    <t>c2mort</t>
   </si>
   <si>
-    <t>CNRALT</t>
+    <t>cnralt</t>
   </si>
   <si>
-    <t>CBKAAM</t>
+    <t>cbkaam</t>
   </si>
   <si>
-    <t>CASIAM</t>
+    <t>casiam</t>
   </si>
   <si>
-    <t>CNHPIM</t>
+    <t>cnhpim</t>
   </si>
   <si>
-    <t>CHISPM</t>
+    <t>chispm</t>
   </si>
   <si>
-    <t>CWHITM</t>
+    <t>cwhitm</t>
   </si>
   <si>
-    <t>CUNKNM</t>
+    <t>cunknm</t>
   </si>
   <si>
-    <t>C2MORM</t>
+    <t>c2morm</t>
   </si>
   <si>
-    <t>CNRALM</t>
+    <t>cnralm</t>
   </si>
   <si>
-    <t>CBKAAW</t>
+    <t>cbkaaw</t>
   </si>
   <si>
-    <t>CASIAW</t>
+    <t>casiaw</t>
   </si>
   <si>
-    <t>CNHPIW</t>
+    <t>cnhpiw</t>
   </si>
   <si>
-    <t>CHISPW</t>
+    <t>chispw</t>
   </si>
   <si>
-    <t>CWHITW</t>
+    <t>cwhitw</t>
   </si>
   <si>
-    <t>CUNKNW</t>
+    <t>cunknw</t>
   </si>
   <si>
-    <t>C2MORW</t>
+    <t>c2morw</t>
   </si>
   <si>
-    <t>CNRALW</t>
+    <t>cnralw</t>
   </si>
   <si>
-    <t>Year</t>
+    <t>majornum</t>
+  </si>
+  <si>
+    <t>year</t>
   </si>
 </sst>
 </file>
@@ -479,10 +482,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AJ406"/>
+  <dimension ref="A1:AK406"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -591,8 +594,11 @@
       <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:36">
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37">
       <c r="A2">
         <v>100654</v>
       </c>
@@ -645,10 +651,13 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK2">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37">
       <c r="A3">
         <v>100663</v>
       </c>
@@ -740,10 +749,13 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK3">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37">
       <c r="A4">
         <v>100663</v>
       </c>
@@ -835,10 +847,13 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK4">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37">
       <c r="A5">
         <v>100706</v>
       </c>
@@ -930,10 +945,13 @@
         <v>2</v>
       </c>
       <c r="AJ5">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37">
       <c r="A6">
         <v>100706</v>
       </c>
@@ -1025,10 +1043,13 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37">
       <c r="A7">
         <v>100751</v>
       </c>
@@ -1081,10 +1102,13 @@
         <v>1</v>
       </c>
       <c r="AJ7">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK7">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37">
       <c r="A8">
         <v>100751</v>
       </c>
@@ -1137,10 +1161,13 @@
         <v>0</v>
       </c>
       <c r="AJ8">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37">
       <c r="A9">
         <v>100858</v>
       </c>
@@ -1193,10 +1220,13 @@
         <v>0</v>
       </c>
       <c r="AJ9">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK9">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37">
       <c r="A10">
         <v>100858</v>
       </c>
@@ -1249,10 +1279,13 @@
         <v>1</v>
       </c>
       <c r="AJ10">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="11" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK10">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
       <c r="A11">
         <v>102614</v>
       </c>
@@ -1344,10 +1377,13 @@
         <v>0</v>
       </c>
       <c r="AJ11">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="12" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK11">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37">
       <c r="A12">
         <v>102614</v>
       </c>
@@ -1439,10 +1475,13 @@
         <v>1</v>
       </c>
       <c r="AJ12">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK12">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37">
       <c r="A13">
         <v>104151</v>
       </c>
@@ -1495,10 +1534,13 @@
         <v>0</v>
       </c>
       <c r="AJ13">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK13">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37">
       <c r="A14">
         <v>104151</v>
       </c>
@@ -1551,10 +1593,13 @@
         <v>0</v>
       </c>
       <c r="AJ14">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK14">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37">
       <c r="A15">
         <v>104179</v>
       </c>
@@ -1646,10 +1691,13 @@
         <v>1</v>
       </c>
       <c r="AJ15">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="16" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK15">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37">
       <c r="A16">
         <v>104179</v>
       </c>
@@ -1741,10 +1789,13 @@
         <v>3</v>
       </c>
       <c r="AJ16">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="17" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK16">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37">
       <c r="A17">
         <v>105330</v>
       </c>
@@ -1836,10 +1887,13 @@
         <v>0</v>
       </c>
       <c r="AJ17">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="18" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK17">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37">
       <c r="A18">
         <v>106397</v>
       </c>
@@ -1931,10 +1985,13 @@
         <v>0</v>
       </c>
       <c r="AJ18">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="19" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK18">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37">
       <c r="A19">
         <v>106397</v>
       </c>
@@ -2026,10 +2083,13 @@
         <v>0</v>
       </c>
       <c r="AJ19">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="20" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK19">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37">
       <c r="A20">
         <v>110404</v>
       </c>
@@ -2082,10 +2142,13 @@
         <v>1</v>
       </c>
       <c r="AJ20">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="21" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK20">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37">
       <c r="A21">
         <v>110404</v>
       </c>
@@ -2138,10 +2201,13 @@
         <v>2</v>
       </c>
       <c r="AJ21">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="22" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK21">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37">
       <c r="A22">
         <v>110556</v>
       </c>
@@ -2194,10 +2260,13 @@
         <v>0</v>
       </c>
       <c r="AJ22">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="23" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK22">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37">
       <c r="A23">
         <v>110565</v>
       </c>
@@ -2250,10 +2319,13 @@
         <v>0</v>
       </c>
       <c r="AJ23">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="24" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK23">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37">
       <c r="A24">
         <v>110583</v>
       </c>
@@ -2306,10 +2378,13 @@
         <v>0</v>
       </c>
       <c r="AJ24">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="25" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK24">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37">
       <c r="A25">
         <v>110592</v>
       </c>
@@ -2362,10 +2437,13 @@
         <v>0</v>
       </c>
       <c r="AJ25">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="26" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK25">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37">
       <c r="A26">
         <v>110608</v>
       </c>
@@ -2418,10 +2496,13 @@
         <v>3</v>
       </c>
       <c r="AJ26">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="27" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK26">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37">
       <c r="A27">
         <v>110635</v>
       </c>
@@ -2474,10 +2555,13 @@
         <v>2</v>
       </c>
       <c r="AJ27">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="28" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK27">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37">
       <c r="A28">
         <v>110635</v>
       </c>
@@ -2530,10 +2614,13 @@
         <v>1</v>
       </c>
       <c r="AJ28">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="29" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK28">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37">
       <c r="A29">
         <v>110644</v>
       </c>
@@ -2586,10 +2673,13 @@
         <v>0</v>
       </c>
       <c r="AJ29">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="30" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK29">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37">
       <c r="A30">
         <v>110644</v>
       </c>
@@ -2642,10 +2732,13 @@
         <v>0</v>
       </c>
       <c r="AJ30">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="31" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK30">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37">
       <c r="A31">
         <v>110653</v>
       </c>
@@ -2698,10 +2791,13 @@
         <v>0</v>
       </c>
       <c r="AJ31">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="32" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK31">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37">
       <c r="A32">
         <v>110653</v>
       </c>
@@ -2754,10 +2850,13 @@
         <v>3</v>
       </c>
       <c r="AJ32">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="33" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK32">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37">
       <c r="A33">
         <v>110662</v>
       </c>
@@ -2810,10 +2909,13 @@
         <v>1</v>
       </c>
       <c r="AJ33">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="34" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK33">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37">
       <c r="A34">
         <v>110662</v>
       </c>
@@ -2866,10 +2968,13 @@
         <v>0</v>
       </c>
       <c r="AJ34">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="35" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK34">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37">
       <c r="A35">
         <v>110671</v>
       </c>
@@ -2922,10 +3027,13 @@
         <v>0</v>
       </c>
       <c r="AJ35">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="36" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK35">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37">
       <c r="A36">
         <v>110671</v>
       </c>
@@ -2978,10 +3086,13 @@
         <v>0</v>
       </c>
       <c r="AJ36">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="37" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK36">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37">
       <c r="A37">
         <v>110680</v>
       </c>
@@ -3034,10 +3145,13 @@
         <v>0</v>
       </c>
       <c r="AJ37">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="38" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK37">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="38" spans="1:37">
       <c r="A38">
         <v>110680</v>
       </c>
@@ -3090,10 +3204,13 @@
         <v>0</v>
       </c>
       <c r="AJ38">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="39" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK38">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="39" spans="1:37">
       <c r="A39">
         <v>110705</v>
       </c>
@@ -3146,10 +3263,13 @@
         <v>0</v>
       </c>
       <c r="AJ39">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="40" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK39">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="40" spans="1:37">
       <c r="A40">
         <v>110705</v>
       </c>
@@ -3202,10 +3322,13 @@
         <v>1</v>
       </c>
       <c r="AJ40">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="41" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK40">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="41" spans="1:37">
       <c r="A41">
         <v>110714</v>
       </c>
@@ -3258,10 +3381,13 @@
         <v>0</v>
       </c>
       <c r="AJ41">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="42" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK41">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="42" spans="1:37">
       <c r="A42">
         <v>110714</v>
       </c>
@@ -3314,10 +3440,13 @@
         <v>0</v>
       </c>
       <c r="AJ42">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="43" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK42">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="43" spans="1:37">
       <c r="A43">
         <v>119678</v>
       </c>
@@ -3370,10 +3499,13 @@
         <v>0</v>
       </c>
       <c r="AJ43">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="44" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK43">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="44" spans="1:37">
       <c r="A44">
         <v>119678</v>
       </c>
@@ -3426,10 +3558,13 @@
         <v>0</v>
       </c>
       <c r="AJ44">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="45" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK44">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="45" spans="1:37">
       <c r="A45">
         <v>122409</v>
       </c>
@@ -3482,10 +3617,13 @@
         <v>0</v>
       </c>
       <c r="AJ45">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="46" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK45">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="46" spans="1:37">
       <c r="A46">
         <v>122597</v>
       </c>
@@ -3538,10 +3676,13 @@
         <v>0</v>
       </c>
       <c r="AJ46">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="47" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK46">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="47" spans="1:37">
       <c r="A47">
         <v>122755</v>
       </c>
@@ -3594,10 +3735,13 @@
         <v>0</v>
       </c>
       <c r="AJ47">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="48" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK47">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="48" spans="1:37">
       <c r="A48">
         <v>123961</v>
       </c>
@@ -3689,10 +3833,13 @@
         <v>0</v>
       </c>
       <c r="AJ48">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="49" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK48">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="49" spans="1:37">
       <c r="A49">
         <v>123961</v>
       </c>
@@ -3784,10 +3931,13 @@
         <v>0</v>
       </c>
       <c r="AJ49">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="50" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK49">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="50" spans="1:37">
       <c r="A50">
         <v>126614</v>
       </c>
@@ -3840,10 +3990,13 @@
         <v>2</v>
       </c>
       <c r="AJ50">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="51" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK50">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="51" spans="1:37">
       <c r="A51">
         <v>126614</v>
       </c>
@@ -3896,10 +4049,13 @@
         <v>1</v>
       </c>
       <c r="AJ51">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="52" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK51">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="52" spans="1:37">
       <c r="A52">
         <v>126614</v>
       </c>
@@ -3952,10 +4108,13 @@
         <v>0</v>
       </c>
       <c r="AJ52">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="53" spans="1:36">
+        <v>2</v>
+      </c>
+      <c r="AK52">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="53" spans="1:37">
       <c r="A53">
         <v>126775</v>
       </c>
@@ -4008,10 +4167,13 @@
         <v>0</v>
       </c>
       <c r="AJ53">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="54" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK53">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="54" spans="1:37">
       <c r="A54">
         <v>126775</v>
       </c>
@@ -4064,10 +4226,13 @@
         <v>0</v>
       </c>
       <c r="AJ54">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="55" spans="1:36">
+        <v>2</v>
+      </c>
+      <c r="AK54">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="55" spans="1:37">
       <c r="A55">
         <v>126818</v>
       </c>
@@ -4120,10 +4285,13 @@
         <v>1</v>
       </c>
       <c r="AJ55">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="56" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK55">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="56" spans="1:37">
       <c r="A56">
         <v>126818</v>
       </c>
@@ -4176,10 +4344,13 @@
         <v>0</v>
       </c>
       <c r="AJ56">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="57" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK56">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="57" spans="1:37">
       <c r="A57">
         <v>126818</v>
       </c>
@@ -4232,10 +4403,13 @@
         <v>0</v>
       </c>
       <c r="AJ57">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="58" spans="1:36">
+        <v>2</v>
+      </c>
+      <c r="AK57">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="58" spans="1:37">
       <c r="A58">
         <v>127060</v>
       </c>
@@ -4327,10 +4501,13 @@
         <v>1</v>
       </c>
       <c r="AJ58">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="59" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK58">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="59" spans="1:37">
       <c r="A59">
         <v>129020</v>
       </c>
@@ -4383,10 +4560,13 @@
         <v>1</v>
       </c>
       <c r="AJ59">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="60" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK59">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="60" spans="1:37">
       <c r="A60">
         <v>129020</v>
       </c>
@@ -4439,10 +4619,13 @@
         <v>1</v>
       </c>
       <c r="AJ60">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="61" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK60">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="61" spans="1:37">
       <c r="A61">
         <v>130697</v>
       </c>
@@ -4495,10 +4678,13 @@
         <v>0</v>
       </c>
       <c r="AJ61">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="62" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK61">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="62" spans="1:37">
       <c r="A62">
         <v>130697</v>
       </c>
@@ -4551,10 +4737,13 @@
         <v>0</v>
       </c>
       <c r="AJ62">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="63" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK62">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="63" spans="1:37">
       <c r="A63">
         <v>130794</v>
       </c>
@@ -4607,10 +4796,13 @@
         <v>0</v>
       </c>
       <c r="AJ63">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="64" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK63">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="64" spans="1:37">
       <c r="A64">
         <v>130794</v>
       </c>
@@ -4663,10 +4855,13 @@
         <v>2</v>
       </c>
       <c r="AJ64">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="65" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK64">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="65" spans="1:37">
       <c r="A65">
         <v>130934</v>
       </c>
@@ -4719,10 +4914,13 @@
         <v>0</v>
       </c>
       <c r="AJ65">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="66" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK65">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="66" spans="1:37">
       <c r="A66">
         <v>130943</v>
       </c>
@@ -4814,10 +5012,13 @@
         <v>1</v>
       </c>
       <c r="AJ66">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="67" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK66">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="67" spans="1:37">
       <c r="A67">
         <v>130943</v>
       </c>
@@ -4909,10 +5110,13 @@
         <v>1</v>
       </c>
       <c r="AJ67">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="68" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK67">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="68" spans="1:37">
       <c r="A68">
         <v>131283</v>
       </c>
@@ -4965,10 +5169,13 @@
         <v>0</v>
       </c>
       <c r="AJ68">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="69" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK68">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="69" spans="1:37">
       <c r="A69">
         <v>131283</v>
       </c>
@@ -5021,10 +5228,13 @@
         <v>0</v>
       </c>
       <c r="AJ69">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="70" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK69">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="70" spans="1:37">
       <c r="A70">
         <v>131469</v>
       </c>
@@ -5077,10 +5287,13 @@
         <v>1</v>
       </c>
       <c r="AJ70">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="71" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK70">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="71" spans="1:37">
       <c r="A71">
         <v>131469</v>
       </c>
@@ -5133,10 +5346,13 @@
         <v>1</v>
       </c>
       <c r="AJ71">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="72" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK71">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="72" spans="1:37">
       <c r="A72">
         <v>131496</v>
       </c>
@@ -5228,10 +5444,13 @@
         <v>0</v>
       </c>
       <c r="AJ72">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="73" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK72">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="73" spans="1:37">
       <c r="A73">
         <v>131496</v>
       </c>
@@ -5323,10 +5542,13 @@
         <v>2</v>
       </c>
       <c r="AJ73">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="74" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK73">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="74" spans="1:37">
       <c r="A74">
         <v>131520</v>
       </c>
@@ -5379,10 +5601,13 @@
         <v>0</v>
       </c>
       <c r="AJ74">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="75" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK74">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="75" spans="1:37">
       <c r="A75">
         <v>132903</v>
       </c>
@@ -5435,10 +5660,13 @@
         <v>1</v>
       </c>
       <c r="AJ75">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="76" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK75">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="76" spans="1:37">
       <c r="A76">
         <v>132903</v>
       </c>
@@ -5491,10 +5719,13 @@
         <v>1</v>
       </c>
       <c r="AJ76">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="77" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK76">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="77" spans="1:37">
       <c r="A77">
         <v>133650</v>
       </c>
@@ -5547,10 +5778,13 @@
         <v>0</v>
       </c>
       <c r="AJ77">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="78" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK77">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="78" spans="1:37">
       <c r="A78">
         <v>133650</v>
       </c>
@@ -5603,10 +5837,13 @@
         <v>0</v>
       </c>
       <c r="AJ78">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="79" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK78">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="79" spans="1:37">
       <c r="A79">
         <v>133669</v>
       </c>
@@ -5659,10 +5896,13 @@
         <v>0</v>
       </c>
       <c r="AJ79">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="80" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK79">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="80" spans="1:37">
       <c r="A80">
         <v>133669</v>
       </c>
@@ -5715,10 +5955,13 @@
         <v>1</v>
       </c>
       <c r="AJ80">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="81" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK80">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="81" spans="1:37">
       <c r="A81">
         <v>133881</v>
       </c>
@@ -5810,10 +6053,13 @@
         <v>0</v>
       </c>
       <c r="AJ81">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="82" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK81">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="82" spans="1:37">
       <c r="A82">
         <v>133881</v>
       </c>
@@ -5905,10 +6151,13 @@
         <v>0</v>
       </c>
       <c r="AJ82">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="83" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK82">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="83" spans="1:37">
       <c r="A83">
         <v>133951</v>
       </c>
@@ -5961,10 +6210,13 @@
         <v>0</v>
       </c>
       <c r="AJ83">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="84" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK83">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="84" spans="1:37">
       <c r="A84">
         <v>133951</v>
       </c>
@@ -6017,10 +6269,13 @@
         <v>1</v>
       </c>
       <c r="AJ84">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="85" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK84">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="85" spans="1:37">
       <c r="A85">
         <v>134097</v>
       </c>
@@ -6073,10 +6328,13 @@
         <v>1</v>
       </c>
       <c r="AJ85">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="86" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK85">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="86" spans="1:37">
       <c r="A86">
         <v>134097</v>
       </c>
@@ -6129,10 +6387,13 @@
         <v>1</v>
       </c>
       <c r="AJ86">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="87" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK86">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="87" spans="1:37">
       <c r="A87">
         <v>134130</v>
       </c>
@@ -6185,10 +6446,13 @@
         <v>1</v>
       </c>
       <c r="AJ87">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="88" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK87">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="88" spans="1:37">
       <c r="A88">
         <v>134130</v>
       </c>
@@ -6241,10 +6505,13 @@
         <v>0</v>
       </c>
       <c r="AJ88">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="89" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK88">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="89" spans="1:37">
       <c r="A89">
         <v>135726</v>
       </c>
@@ -6297,10 +6564,13 @@
         <v>0</v>
       </c>
       <c r="AJ89">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="90" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK89">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="90" spans="1:37">
       <c r="A90">
         <v>135726</v>
       </c>
@@ -6353,10 +6623,13 @@
         <v>0</v>
       </c>
       <c r="AJ90">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="91" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK90">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="91" spans="1:37">
       <c r="A91">
         <v>137351</v>
       </c>
@@ -6409,10 +6682,13 @@
         <v>1</v>
       </c>
       <c r="AJ91">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="92" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK91">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="92" spans="1:37">
       <c r="A92">
         <v>137351</v>
       </c>
@@ -6465,10 +6741,13 @@
         <v>1</v>
       </c>
       <c r="AJ92">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="93" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK92">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="93" spans="1:37">
       <c r="A93">
         <v>138947</v>
       </c>
@@ -6560,10 +6839,13 @@
         <v>0</v>
       </c>
       <c r="AJ93">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="94" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK93">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="94" spans="1:37">
       <c r="A94">
         <v>139658</v>
       </c>
@@ -6616,10 +6898,13 @@
         <v>0</v>
       </c>
       <c r="AJ94">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="95" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK94">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="95" spans="1:37">
       <c r="A95">
         <v>139658</v>
       </c>
@@ -6672,10 +6957,13 @@
         <v>0</v>
       </c>
       <c r="AJ95">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="96" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK95">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="96" spans="1:37">
       <c r="A96">
         <v>139755</v>
       </c>
@@ -6767,10 +7055,13 @@
         <v>0</v>
       </c>
       <c r="AJ96">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="97" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK96">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="97" spans="1:37">
       <c r="A97">
         <v>139755</v>
       </c>
@@ -6862,10 +7153,13 @@
         <v>1</v>
       </c>
       <c r="AJ97">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="98" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK97">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="98" spans="1:37">
       <c r="A98">
         <v>139940</v>
       </c>
@@ -6957,10 +7251,13 @@
         <v>2</v>
       </c>
       <c r="AJ98">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="99" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK98">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="99" spans="1:37">
       <c r="A99">
         <v>139940</v>
       </c>
@@ -7052,10 +7349,13 @@
         <v>3</v>
       </c>
       <c r="AJ99">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="100" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK99">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="100" spans="1:37">
       <c r="A100">
         <v>139959</v>
       </c>
@@ -7147,10 +7447,13 @@
         <v>0</v>
       </c>
       <c r="AJ100">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="101" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK100">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="101" spans="1:37">
       <c r="A101">
         <v>139959</v>
       </c>
@@ -7242,10 +7545,13 @@
         <v>3</v>
       </c>
       <c r="AJ101">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="102" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK101">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="102" spans="1:37">
       <c r="A102">
         <v>141574</v>
       </c>
@@ -7298,10 +7604,13 @@
         <v>0</v>
       </c>
       <c r="AJ102">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="103" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK102">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="103" spans="1:37">
       <c r="A103">
         <v>141574</v>
       </c>
@@ -7354,10 +7663,13 @@
         <v>0</v>
       </c>
       <c r="AJ103">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="104" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK103">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="104" spans="1:37">
       <c r="A104">
         <v>142276</v>
       </c>
@@ -7410,10 +7722,13 @@
         <v>0</v>
       </c>
       <c r="AJ104">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="105" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK104">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="105" spans="1:37">
       <c r="A105">
         <v>142276</v>
       </c>
@@ -7466,10 +7781,13 @@
         <v>1</v>
       </c>
       <c r="AJ105">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="106" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK105">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="106" spans="1:37">
       <c r="A106">
         <v>142285</v>
       </c>
@@ -7561,10 +7879,13 @@
         <v>2</v>
       </c>
       <c r="AJ106">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="107" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK106">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="107" spans="1:37">
       <c r="A107">
         <v>142285</v>
       </c>
@@ -7656,10 +7977,13 @@
         <v>0</v>
       </c>
       <c r="AJ107">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="108" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK107">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="108" spans="1:37">
       <c r="A108">
         <v>144050</v>
       </c>
@@ -7751,10 +8075,13 @@
         <v>1</v>
       </c>
       <c r="AJ108">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="109" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK108">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="109" spans="1:37">
       <c r="A109">
         <v>144050</v>
       </c>
@@ -7846,10 +8173,13 @@
         <v>0</v>
       </c>
       <c r="AJ109">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="110" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK109">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="110" spans="1:37">
       <c r="A110">
         <v>144740</v>
       </c>
@@ -7941,10 +8271,13 @@
         <v>0</v>
       </c>
       <c r="AJ110">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="111" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK110">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="111" spans="1:37">
       <c r="A111">
         <v>144740</v>
       </c>
@@ -8036,10 +8369,13 @@
         <v>0</v>
       </c>
       <c r="AJ111">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="112" spans="1:36">
+        <v>2</v>
+      </c>
+      <c r="AK111">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="112" spans="1:37">
       <c r="A112">
         <v>145600</v>
       </c>
@@ -8092,10 +8428,13 @@
         <v>1</v>
       </c>
       <c r="AJ112">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="113" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK112">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="113" spans="1:37">
       <c r="A113">
         <v>145600</v>
       </c>
@@ -8148,10 +8487,13 @@
         <v>1</v>
       </c>
       <c r="AJ113">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="114" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK113">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="114" spans="1:37">
       <c r="A114">
         <v>145637</v>
       </c>
@@ -8204,10 +8546,13 @@
         <v>0</v>
       </c>
       <c r="AJ114">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="115" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK114">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="115" spans="1:37">
       <c r="A115">
         <v>145637</v>
       </c>
@@ -8260,10 +8605,13 @@
         <v>7</v>
       </c>
       <c r="AJ115">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="116" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK115">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="116" spans="1:37">
       <c r="A116">
         <v>145725</v>
       </c>
@@ -8316,10 +8664,13 @@
         <v>1</v>
       </c>
       <c r="AJ116">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="117" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK116">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="117" spans="1:37">
       <c r="A117">
         <v>145725</v>
       </c>
@@ -8372,10 +8723,13 @@
         <v>1</v>
       </c>
       <c r="AJ117">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="118" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK117">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="118" spans="1:37">
       <c r="A118">
         <v>147703</v>
       </c>
@@ -8428,10 +8782,13 @@
         <v>1</v>
       </c>
       <c r="AJ118">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="119" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK118">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="119" spans="1:37">
       <c r="A119">
         <v>147703</v>
       </c>
@@ -8484,10 +8841,13 @@
         <v>1</v>
       </c>
       <c r="AJ119">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="120" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK119">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="120" spans="1:37">
       <c r="A120">
         <v>149222</v>
       </c>
@@ -8579,10 +8939,13 @@
         <v>1</v>
       </c>
       <c r="AJ120">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="121" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK120">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="121" spans="1:37">
       <c r="A121">
         <v>149222</v>
       </c>
@@ -8674,10 +9037,13 @@
         <v>0</v>
       </c>
       <c r="AJ121">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="122" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK121">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="122" spans="1:37">
       <c r="A122">
         <v>149222</v>
       </c>
@@ -8769,10 +9135,13 @@
         <v>0</v>
       </c>
       <c r="AJ122">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="123" spans="1:36">
+        <v>2</v>
+      </c>
+      <c r="AK122">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="123" spans="1:37">
       <c r="A123">
         <v>149222</v>
       </c>
@@ -8864,10 +9233,13 @@
         <v>0</v>
       </c>
       <c r="AJ123">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="124" spans="1:36">
+        <v>2</v>
+      </c>
+      <c r="AK123">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="124" spans="1:37">
       <c r="A124">
         <v>149231</v>
       </c>
@@ -8920,10 +9292,13 @@
         <v>0</v>
       </c>
       <c r="AJ124">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="125" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK124">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="125" spans="1:37">
       <c r="A125">
         <v>149772</v>
       </c>
@@ -9015,10 +9390,13 @@
         <v>1</v>
       </c>
       <c r="AJ125">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="126" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK125">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="126" spans="1:37">
       <c r="A126">
         <v>150136</v>
       </c>
@@ -9110,10 +9488,13 @@
         <v>0</v>
       </c>
       <c r="AJ126">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="127" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK126">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="127" spans="1:37">
       <c r="A127">
         <v>151111</v>
       </c>
@@ -9205,10 +9586,13 @@
         <v>1</v>
       </c>
       <c r="AJ127">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="128" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK127">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="128" spans="1:37">
       <c r="A128">
         <v>151351</v>
       </c>
@@ -9300,10 +9684,13 @@
         <v>1</v>
       </c>
       <c r="AJ128">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="129" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK128">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="129" spans="1:37">
       <c r="A129">
         <v>151351</v>
       </c>
@@ -9395,10 +9782,13 @@
         <v>2</v>
       </c>
       <c r="AJ129">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="130" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK129">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="130" spans="1:37">
       <c r="A130">
         <v>152080</v>
       </c>
@@ -9451,10 +9841,13 @@
         <v>1</v>
       </c>
       <c r="AJ130">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="131" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK130">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="131" spans="1:37">
       <c r="A131">
         <v>152080</v>
       </c>
@@ -9507,10 +9900,13 @@
         <v>1</v>
       </c>
       <c r="AJ131">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="132" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK131">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="132" spans="1:37">
       <c r="A132">
         <v>153658</v>
       </c>
@@ -9563,10 +9959,13 @@
         <v>0</v>
       </c>
       <c r="AJ132">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="133" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK132">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="133" spans="1:37">
       <c r="A133">
         <v>153658</v>
       </c>
@@ -9619,10 +10018,13 @@
         <v>0</v>
       </c>
       <c r="AJ133">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="134" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK133">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="134" spans="1:37">
       <c r="A134">
         <v>155317</v>
       </c>
@@ -9675,10 +10077,13 @@
         <v>0</v>
       </c>
       <c r="AJ134">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="135" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK134">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="135" spans="1:37">
       <c r="A135">
         <v>155317</v>
       </c>
@@ -9731,10 +10136,13 @@
         <v>0</v>
       </c>
       <c r="AJ135">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="136" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK135">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="136" spans="1:37">
       <c r="A136">
         <v>155399</v>
       </c>
@@ -9787,10 +10195,13 @@
         <v>1</v>
       </c>
       <c r="AJ136">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="137" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK136">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="137" spans="1:37">
       <c r="A137">
         <v>155399</v>
       </c>
@@ -9843,10 +10254,13 @@
         <v>4</v>
       </c>
       <c r="AJ137">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="138" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK137">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="138" spans="1:37">
       <c r="A138">
         <v>155681</v>
       </c>
@@ -9899,10 +10313,13 @@
         <v>0</v>
       </c>
       <c r="AJ138">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="139" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK138">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="139" spans="1:37">
       <c r="A139">
         <v>157085</v>
       </c>
@@ -9994,10 +10411,13 @@
         <v>2</v>
       </c>
       <c r="AJ139">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="140" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK139">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="140" spans="1:37">
       <c r="A140">
         <v>157085</v>
       </c>
@@ -10089,10 +10509,13 @@
         <v>1</v>
       </c>
       <c r="AJ140">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="141" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK140">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="141" spans="1:37">
       <c r="A141">
         <v>157289</v>
       </c>
@@ -10145,10 +10568,13 @@
         <v>0</v>
       </c>
       <c r="AJ141">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="142" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK141">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="142" spans="1:37">
       <c r="A142">
         <v>159391</v>
       </c>
@@ -10240,10 +10666,13 @@
         <v>0</v>
       </c>
       <c r="AJ142">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="143" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK142">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="143" spans="1:37">
       <c r="A143">
         <v>159391</v>
       </c>
@@ -10335,10 +10764,13 @@
         <v>0</v>
       </c>
       <c r="AJ143">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="144" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK143">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="144" spans="1:37">
       <c r="A144">
         <v>159647</v>
       </c>
@@ -10430,10 +10862,13 @@
         <v>0</v>
       </c>
       <c r="AJ144">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="145" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK144">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="145" spans="1:37">
       <c r="A145">
         <v>159939</v>
       </c>
@@ -10525,10 +10960,13 @@
         <v>0</v>
       </c>
       <c r="AJ145">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="146" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK145">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="146" spans="1:37">
       <c r="A146">
         <v>160621</v>
       </c>
@@ -10620,10 +11058,13 @@
         <v>0</v>
       </c>
       <c r="AJ146">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="147" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK146">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="147" spans="1:37">
       <c r="A147">
         <v>160658</v>
       </c>
@@ -10715,10 +11156,13 @@
         <v>2</v>
       </c>
       <c r="AJ147">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="148" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK147">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="148" spans="1:37">
       <c r="A148">
         <v>160755</v>
       </c>
@@ -10810,10 +11254,13 @@
         <v>0</v>
       </c>
       <c r="AJ148">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="149" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK148">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="149" spans="1:37">
       <c r="A149">
         <v>160755</v>
       </c>
@@ -10905,10 +11352,13 @@
         <v>0</v>
       </c>
       <c r="AJ149">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="150" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK149">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="150" spans="1:37">
       <c r="A150">
         <v>161253</v>
       </c>
@@ -10961,10 +11411,13 @@
         <v>0</v>
       </c>
       <c r="AJ150">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="151" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK150">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="151" spans="1:37">
       <c r="A151">
         <v>161253</v>
       </c>
@@ -11017,10 +11470,13 @@
         <v>0</v>
       </c>
       <c r="AJ151">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="152" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK151">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="152" spans="1:37">
       <c r="A152">
         <v>162928</v>
       </c>
@@ -11073,10 +11529,13 @@
         <v>0</v>
       </c>
       <c r="AJ152">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="153" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK152">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="153" spans="1:37">
       <c r="A153">
         <v>162928</v>
       </c>
@@ -11129,10 +11588,13 @@
         <v>0</v>
       </c>
       <c r="AJ153">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="154" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK153">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="154" spans="1:37">
       <c r="A154">
         <v>163268</v>
       </c>
@@ -11185,10 +11647,13 @@
         <v>2</v>
       </c>
       <c r="AJ154">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="155" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK154">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="155" spans="1:37">
       <c r="A155">
         <v>163268</v>
       </c>
@@ -11241,10 +11706,13 @@
         <v>0</v>
       </c>
       <c r="AJ155">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="156" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK155">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="156" spans="1:37">
       <c r="A156">
         <v>163286</v>
       </c>
@@ -11297,10 +11765,13 @@
         <v>0</v>
       </c>
       <c r="AJ156">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="157" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK156">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="157" spans="1:37">
       <c r="A157">
         <v>163286</v>
       </c>
@@ -11353,10 +11824,13 @@
         <v>2</v>
       </c>
       <c r="AJ157">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="158" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK157">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="158" spans="1:37">
       <c r="A158">
         <v>164924</v>
       </c>
@@ -11409,10 +11883,13 @@
         <v>1</v>
       </c>
       <c r="AJ158">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="159" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK158">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="159" spans="1:37">
       <c r="A159">
         <v>164924</v>
       </c>
@@ -11465,10 +11942,13 @@
         <v>1</v>
       </c>
       <c r="AJ159">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="160" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK159">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="160" spans="1:37">
       <c r="A160">
         <v>164988</v>
       </c>
@@ -11521,10 +12001,13 @@
         <v>0</v>
       </c>
       <c r="AJ160">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="161" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK160">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="161" spans="1:37">
       <c r="A161">
         <v>164988</v>
       </c>
@@ -11577,10 +12060,13 @@
         <v>1</v>
       </c>
       <c r="AJ161">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="162" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK161">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="162" spans="1:37">
       <c r="A162">
         <v>165015</v>
       </c>
@@ -11672,10 +12158,13 @@
         <v>0</v>
       </c>
       <c r="AJ162">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="163" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK162">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="163" spans="1:37">
       <c r="A163">
         <v>165015</v>
       </c>
@@ -11767,10 +12256,13 @@
         <v>0</v>
       </c>
       <c r="AJ163">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="164" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK163">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="164" spans="1:37">
       <c r="A164">
         <v>165334</v>
       </c>
@@ -11862,10 +12354,13 @@
         <v>0</v>
       </c>
       <c r="AJ164">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="165" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK164">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="165" spans="1:37">
       <c r="A165">
         <v>165334</v>
       </c>
@@ -11957,10 +12452,13 @@
         <v>0</v>
       </c>
       <c r="AJ165">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="166" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK165">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="166" spans="1:37">
       <c r="A166">
         <v>166027</v>
       </c>
@@ -12067,10 +12565,13 @@
         <v>7</v>
       </c>
       <c r="AJ166">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="167" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK166">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="167" spans="1:37">
       <c r="A167">
         <v>166027</v>
       </c>
@@ -12177,10 +12678,13 @@
         <v>6</v>
       </c>
       <c r="AJ167">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="168" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK167">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="168" spans="1:37">
       <c r="A168">
         <v>166513</v>
       </c>
@@ -12272,10 +12776,13 @@
         <v>0</v>
       </c>
       <c r="AJ168">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="169" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK168">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="169" spans="1:37">
       <c r="A169">
         <v>166513</v>
       </c>
@@ -12367,10 +12874,13 @@
         <v>0</v>
       </c>
       <c r="AJ169">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="170" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK169">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="170" spans="1:37">
       <c r="A170">
         <v>166629</v>
       </c>
@@ -12477,10 +12987,13 @@
         <v>0</v>
       </c>
       <c r="AJ170">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="171" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK170">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="171" spans="1:37">
       <c r="A171">
         <v>166629</v>
       </c>
@@ -12587,10 +13100,13 @@
         <v>1</v>
       </c>
       <c r="AJ171">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="172" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK171">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="172" spans="1:37">
       <c r="A172">
         <v>166638</v>
       </c>
@@ -12682,10 +13198,13 @@
         <v>3</v>
       </c>
       <c r="AJ172">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="173" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK172">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="173" spans="1:37">
       <c r="A173">
         <v>166683</v>
       </c>
@@ -12777,10 +13296,13 @@
         <v>0</v>
       </c>
       <c r="AJ173">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="174" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK173">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="174" spans="1:37">
       <c r="A174">
         <v>166683</v>
       </c>
@@ -12872,10 +13394,13 @@
         <v>3</v>
       </c>
       <c r="AJ174">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="175" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK174">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="175" spans="1:37">
       <c r="A175">
         <v>167358</v>
       </c>
@@ -12928,10 +13453,13 @@
         <v>3</v>
       </c>
       <c r="AJ175">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="176" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK175">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="176" spans="1:37">
       <c r="A176">
         <v>167358</v>
       </c>
@@ -12984,10 +13512,13 @@
         <v>1</v>
       </c>
       <c r="AJ176">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="177" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK176">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="177" spans="1:37">
       <c r="A177">
         <v>167987</v>
       </c>
@@ -13079,10 +13610,13 @@
         <v>1</v>
       </c>
       <c r="AJ177">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="178" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK177">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="178" spans="1:37">
       <c r="A178">
         <v>168148</v>
       </c>
@@ -13174,10 +13708,13 @@
         <v>0</v>
       </c>
       <c r="AJ178">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="179" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK178">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="179" spans="1:37">
       <c r="A179">
         <v>168148</v>
       </c>
@@ -13269,10 +13806,13 @@
         <v>0</v>
       </c>
       <c r="AJ179">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="180" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK179">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="180" spans="1:37">
       <c r="A180">
         <v>168421</v>
       </c>
@@ -13325,10 +13865,13 @@
         <v>1</v>
       </c>
       <c r="AJ180">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="181" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK180">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="181" spans="1:37">
       <c r="A181">
         <v>168421</v>
       </c>
@@ -13381,10 +13924,13 @@
         <v>0</v>
       </c>
       <c r="AJ181">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="182" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK181">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="182" spans="1:37">
       <c r="A182">
         <v>169248</v>
       </c>
@@ -13437,10 +13983,13 @@
         <v>1</v>
       </c>
       <c r="AJ182">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="183" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK182">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="183" spans="1:37">
       <c r="A183">
         <v>169798</v>
       </c>
@@ -13532,10 +14081,13 @@
         <v>0</v>
       </c>
       <c r="AJ183">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="184" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK183">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="184" spans="1:37">
       <c r="A184">
         <v>170976</v>
       </c>
@@ -13627,10 +14179,13 @@
         <v>0</v>
       </c>
       <c r="AJ184">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="185" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK184">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="185" spans="1:37">
       <c r="A185">
         <v>170976</v>
       </c>
@@ -13722,10 +14277,13 @@
         <v>4</v>
       </c>
       <c r="AJ185">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="186" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK185">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="186" spans="1:37">
       <c r="A186">
         <v>171100</v>
       </c>
@@ -13778,10 +14336,13 @@
         <v>1</v>
       </c>
       <c r="AJ186">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="187" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK186">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="187" spans="1:37">
       <c r="A187">
         <v>171100</v>
       </c>
@@ -13834,10 +14395,13 @@
         <v>1</v>
       </c>
       <c r="AJ187">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="188" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK187">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="188" spans="1:37">
       <c r="A188">
         <v>171128</v>
       </c>
@@ -13929,10 +14493,13 @@
         <v>0</v>
       </c>
       <c r="AJ188">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="189" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK188">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="189" spans="1:37">
       <c r="A189">
         <v>171128</v>
       </c>
@@ -14024,10 +14591,13 @@
         <v>1</v>
       </c>
       <c r="AJ189">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="190" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK189">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="190" spans="1:37">
       <c r="A190">
         <v>171571</v>
       </c>
@@ -14080,10 +14650,13 @@
         <v>1</v>
       </c>
       <c r="AJ190">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="191" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK190">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="191" spans="1:37">
       <c r="A191">
         <v>172644</v>
       </c>
@@ -14136,10 +14709,13 @@
         <v>0</v>
       </c>
       <c r="AJ191">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="192" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK191">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="192" spans="1:37">
       <c r="A192">
         <v>172644</v>
       </c>
@@ -14192,10 +14768,13 @@
         <v>0</v>
       </c>
       <c r="AJ192">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="193" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK192">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="193" spans="1:37">
       <c r="A193">
         <v>172699</v>
       </c>
@@ -14248,10 +14827,13 @@
         <v>1</v>
       </c>
       <c r="AJ193">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="194" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK193">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="194" spans="1:37">
       <c r="A194">
         <v>172699</v>
       </c>
@@ -14304,10 +14886,13 @@
         <v>1</v>
       </c>
       <c r="AJ194">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="195" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK194">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="195" spans="1:37">
       <c r="A195">
         <v>173920</v>
       </c>
@@ -14360,10 +14945,13 @@
         <v>0</v>
       </c>
       <c r="AJ195">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="196" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK195">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="196" spans="1:37">
       <c r="A196">
         <v>174066</v>
       </c>
@@ -14455,10 +15043,13 @@
         <v>2</v>
       </c>
       <c r="AJ196">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="197" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK196">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="197" spans="1:37">
       <c r="A197">
         <v>174066</v>
       </c>
@@ -14550,10 +15141,13 @@
         <v>0</v>
       </c>
       <c r="AJ197">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="198" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK197">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="198" spans="1:37">
       <c r="A198">
         <v>174233</v>
       </c>
@@ -14645,10 +15239,13 @@
         <v>0</v>
       </c>
       <c r="AJ198">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="199" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK198">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="199" spans="1:37">
       <c r="A199">
         <v>176017</v>
       </c>
@@ -14701,10 +15298,13 @@
         <v>0</v>
       </c>
       <c r="AJ199">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="200" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK199">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="200" spans="1:37">
       <c r="A200">
         <v>176017</v>
       </c>
@@ -14757,10 +15357,13 @@
         <v>2</v>
       </c>
       <c r="AJ200">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="201" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK200">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="201" spans="1:37">
       <c r="A201">
         <v>176080</v>
       </c>
@@ -14813,10 +15416,13 @@
         <v>2</v>
       </c>
       <c r="AJ201">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="202" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK201">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="202" spans="1:37">
       <c r="A202">
         <v>176372</v>
       </c>
@@ -14908,10 +15514,13 @@
         <v>0</v>
       </c>
       <c r="AJ202">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="203" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK202">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="203" spans="1:37">
       <c r="A203">
         <v>178396</v>
       </c>
@@ -15003,10 +15612,13 @@
         <v>0</v>
       </c>
       <c r="AJ203">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="204" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK203">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="204" spans="1:37">
       <c r="A204">
         <v>178396</v>
       </c>
@@ -15098,10 +15710,13 @@
         <v>0</v>
       </c>
       <c r="AJ204">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="205" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK204">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="205" spans="1:37">
       <c r="A205">
         <v>178402</v>
       </c>
@@ -15193,10 +15808,13 @@
         <v>1</v>
       </c>
       <c r="AJ205">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="206" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK205">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="206" spans="1:37">
       <c r="A206">
         <v>178411</v>
       </c>
@@ -15288,10 +15906,13 @@
         <v>0</v>
       </c>
       <c r="AJ206">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="207" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK206">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="207" spans="1:37">
       <c r="A207">
         <v>178411</v>
       </c>
@@ -15383,10 +16004,13 @@
         <v>2</v>
       </c>
       <c r="AJ207">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="208" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK207">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="208" spans="1:37">
       <c r="A208">
         <v>178420</v>
       </c>
@@ -15478,10 +16102,13 @@
         <v>2</v>
       </c>
       <c r="AJ208">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="209" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK208">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="209" spans="1:37">
       <c r="A209">
         <v>178420</v>
       </c>
@@ -15573,10 +16200,13 @@
         <v>1</v>
       </c>
       <c r="AJ209">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="210" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK209">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="210" spans="1:37">
       <c r="A210">
         <v>179867</v>
       </c>
@@ -15629,10 +16259,13 @@
         <v>0</v>
       </c>
       <c r="AJ210">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="211" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK210">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="211" spans="1:37">
       <c r="A211">
         <v>179867</v>
       </c>
@@ -15685,10 +16318,13 @@
         <v>2</v>
       </c>
       <c r="AJ211">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="212" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK211">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="212" spans="1:37">
       <c r="A212">
         <v>180461</v>
       </c>
@@ -15741,10 +16377,13 @@
         <v>1</v>
       </c>
       <c r="AJ212">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="213" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK212">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="213" spans="1:37">
       <c r="A213">
         <v>180461</v>
       </c>
@@ -15797,10 +16436,13 @@
         <v>0</v>
       </c>
       <c r="AJ213">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="214" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK213">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="214" spans="1:37">
       <c r="A214">
         <v>180489</v>
       </c>
@@ -15853,10 +16495,13 @@
         <v>0</v>
       </c>
       <c r="AJ214">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="215" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK214">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="215" spans="1:37">
       <c r="A215">
         <v>181002</v>
       </c>
@@ -15909,10 +16554,13 @@
         <v>0</v>
       </c>
       <c r="AJ215">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="216" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK215">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="216" spans="1:37">
       <c r="A216">
         <v>181464</v>
       </c>
@@ -15965,10 +16613,13 @@
         <v>0</v>
       </c>
       <c r="AJ216">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="217" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK216">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="217" spans="1:37">
       <c r="A217">
         <v>181464</v>
       </c>
@@ -16021,10 +16672,13 @@
         <v>0</v>
       </c>
       <c r="AJ217">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="218" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK217">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="218" spans="1:37">
       <c r="A218">
         <v>182281</v>
       </c>
@@ -16116,10 +16770,13 @@
         <v>0</v>
       </c>
       <c r="AJ218">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="219" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK218">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="219" spans="1:37">
       <c r="A219">
         <v>182281</v>
       </c>
@@ -16211,10 +16868,13 @@
         <v>0</v>
       </c>
       <c r="AJ219">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="220" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK219">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="220" spans="1:37">
       <c r="A220">
         <v>182290</v>
       </c>
@@ -16306,10 +16966,13 @@
         <v>1</v>
       </c>
       <c r="AJ220">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="221" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK220">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="221" spans="1:37">
       <c r="A221">
         <v>182290</v>
       </c>
@@ -16401,10 +17064,13 @@
         <v>2</v>
       </c>
       <c r="AJ221">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="222" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK221">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="222" spans="1:37">
       <c r="A222">
         <v>182670</v>
       </c>
@@ -16457,10 +17123,13 @@
         <v>0</v>
       </c>
       <c r="AJ222">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="223" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK222">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="223" spans="1:37">
       <c r="A223">
         <v>182670</v>
       </c>
@@ -16513,10 +17182,13 @@
         <v>0</v>
       </c>
       <c r="AJ223">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="224" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK223">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="224" spans="1:37">
       <c r="A224">
         <v>183044</v>
       </c>
@@ -16569,10 +17241,13 @@
         <v>1</v>
       </c>
       <c r="AJ224">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="225" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK224">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="225" spans="1:37">
       <c r="A225">
         <v>183044</v>
       </c>
@@ -16625,10 +17300,13 @@
         <v>0</v>
       </c>
       <c r="AJ225">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="226" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK225">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="226" spans="1:37">
       <c r="A226">
         <v>186131</v>
       </c>
@@ -16720,10 +17398,13 @@
         <v>2</v>
       </c>
       <c r="AJ226">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="227" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK226">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="227" spans="1:37">
       <c r="A227">
         <v>186131</v>
       </c>
@@ -16815,10 +17496,13 @@
         <v>3</v>
       </c>
       <c r="AJ227">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="228" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK227">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="228" spans="1:37">
       <c r="A228">
         <v>186399</v>
       </c>
@@ -16910,10 +17594,13 @@
         <v>0</v>
       </c>
       <c r="AJ228">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="229" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK228">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="229" spans="1:37">
       <c r="A229">
         <v>186867</v>
       </c>
@@ -17005,10 +17692,13 @@
         <v>1</v>
       </c>
       <c r="AJ229">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="230" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK229">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="230" spans="1:37">
       <c r="A230">
         <v>186867</v>
       </c>
@@ -17100,10 +17790,13 @@
         <v>1</v>
       </c>
       <c r="AJ230">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="231" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK230">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="231" spans="1:37">
       <c r="A231">
         <v>187967</v>
       </c>
@@ -17156,10 +17849,13 @@
         <v>0</v>
       </c>
       <c r="AJ231">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="232" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK231">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="232" spans="1:37">
       <c r="A232">
         <v>187967</v>
       </c>
@@ -17212,10 +17908,13 @@
         <v>0</v>
       </c>
       <c r="AJ232">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="233" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK232">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="233" spans="1:37">
       <c r="A233">
         <v>187985</v>
       </c>
@@ -17307,10 +18006,13 @@
         <v>0</v>
       </c>
       <c r="AJ233">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="234" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK233">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="234" spans="1:37">
       <c r="A234">
         <v>187985</v>
       </c>
@@ -17402,10 +18104,13 @@
         <v>1</v>
       </c>
       <c r="AJ234">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="235" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK234">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="235" spans="1:37">
       <c r="A235">
         <v>188030</v>
       </c>
@@ -17458,10 +18163,13 @@
         <v>2</v>
       </c>
       <c r="AJ235">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="236" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK235">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="236" spans="1:37">
       <c r="A236">
         <v>188030</v>
       </c>
@@ -17514,10 +18222,13 @@
         <v>0</v>
       </c>
       <c r="AJ236">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="237" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK236">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="237" spans="1:37">
       <c r="A237">
         <v>190044</v>
       </c>
@@ -17570,10 +18281,13 @@
         <v>0</v>
       </c>
       <c r="AJ237">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="238" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK237">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="238" spans="1:37">
       <c r="A238">
         <v>190044</v>
       </c>
@@ -17626,10 +18340,13 @@
         <v>0</v>
       </c>
       <c r="AJ238">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="239" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK238">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="239" spans="1:37">
       <c r="A239">
         <v>190150</v>
       </c>
@@ -17721,10 +18438,13 @@
         <v>4</v>
       </c>
       <c r="AJ239">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="240" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK239">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="240" spans="1:37">
       <c r="A240">
         <v>190150</v>
       </c>
@@ -17816,10 +18536,13 @@
         <v>2</v>
       </c>
       <c r="AJ240">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="241" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK240">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="241" spans="1:37">
       <c r="A241">
         <v>190415</v>
       </c>
@@ -17911,10 +18634,13 @@
         <v>2</v>
       </c>
       <c r="AJ241">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="242" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK241">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="242" spans="1:37">
       <c r="A242">
         <v>190415</v>
       </c>
@@ -18006,10 +18732,13 @@
         <v>1</v>
       </c>
       <c r="AJ242">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="243" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK242">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="243" spans="1:37">
       <c r="A243">
         <v>190567</v>
       </c>
@@ -18062,10 +18791,13 @@
         <v>0</v>
       </c>
       <c r="AJ243">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="244" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK243">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="244" spans="1:37">
       <c r="A244">
         <v>190576</v>
       </c>
@@ -18118,10 +18850,13 @@
         <v>1</v>
       </c>
       <c r="AJ244">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="245" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK244">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="245" spans="1:37">
       <c r="A245">
         <v>190576</v>
       </c>
@@ -18174,10 +18909,13 @@
         <v>2</v>
       </c>
       <c r="AJ245">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="246" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK245">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="246" spans="1:37">
       <c r="A246">
         <v>190594</v>
       </c>
@@ -18230,10 +18968,13 @@
         <v>0</v>
       </c>
       <c r="AJ246">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="247" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK246">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="247" spans="1:37">
       <c r="A247">
         <v>190664</v>
       </c>
@@ -18286,10 +19027,13 @@
         <v>0</v>
       </c>
       <c r="AJ247">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="248" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK247">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="248" spans="1:37">
       <c r="A248">
         <v>193900</v>
       </c>
@@ -18342,10 +19086,13 @@
         <v>0</v>
       </c>
       <c r="AJ248">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="249" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK248">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="249" spans="1:37">
       <c r="A249">
         <v>193900</v>
       </c>
@@ -18398,10 +19145,13 @@
         <v>0</v>
       </c>
       <c r="AJ249">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="250" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK249">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="250" spans="1:37">
       <c r="A250">
         <v>194824</v>
       </c>
@@ -18493,10 +19243,13 @@
         <v>0</v>
       </c>
       <c r="AJ250">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="251" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK250">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="251" spans="1:37">
       <c r="A251">
         <v>194824</v>
       </c>
@@ -18588,10 +19341,13 @@
         <v>0</v>
       </c>
       <c r="AJ251">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="252" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK251">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="252" spans="1:37">
       <c r="A252">
         <v>195030</v>
       </c>
@@ -18644,10 +19400,13 @@
         <v>2</v>
       </c>
       <c r="AJ252">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="253" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK252">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="253" spans="1:37">
       <c r="A253">
         <v>195030</v>
       </c>
@@ -18700,10 +19459,13 @@
         <v>2</v>
       </c>
       <c r="AJ253">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="254" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK253">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="254" spans="1:37">
       <c r="A254">
         <v>196060</v>
       </c>
@@ -18756,10 +19518,13 @@
         <v>1</v>
       </c>
       <c r="AJ254">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="255" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK254">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="255" spans="1:37">
       <c r="A255">
         <v>196060</v>
       </c>
@@ -18812,10 +19577,13 @@
         <v>0</v>
       </c>
       <c r="AJ255">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="256" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK255">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="256" spans="1:37">
       <c r="A256">
         <v>196079</v>
       </c>
@@ -18868,10 +19636,13 @@
         <v>0</v>
       </c>
       <c r="AJ256">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="257" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK256">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="257" spans="1:37">
       <c r="A257">
         <v>196088</v>
       </c>
@@ -18924,10 +19695,13 @@
         <v>0</v>
       </c>
       <c r="AJ257">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="258" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK257">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="258" spans="1:37">
       <c r="A258">
         <v>196088</v>
       </c>
@@ -18980,10 +19754,13 @@
         <v>0</v>
       </c>
       <c r="AJ258">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="259" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK258">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="259" spans="1:37">
       <c r="A259">
         <v>196097</v>
       </c>
@@ -19036,10 +19813,13 @@
         <v>0</v>
       </c>
       <c r="AJ259">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="260" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK259">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="260" spans="1:37">
       <c r="A260">
         <v>196097</v>
       </c>
@@ -19092,10 +19872,13 @@
         <v>2</v>
       </c>
       <c r="AJ260">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="261" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK260">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="261" spans="1:37">
       <c r="A261">
         <v>196413</v>
       </c>
@@ -19187,10 +19970,13 @@
         <v>1</v>
       </c>
       <c r="AJ261">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="262" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK261">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="262" spans="1:37">
       <c r="A262">
         <v>196413</v>
       </c>
@@ -19282,10 +20068,13 @@
         <v>1</v>
       </c>
       <c r="AJ262">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="263" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK262">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="263" spans="1:37">
       <c r="A263">
         <v>197869</v>
       </c>
@@ -19377,10 +20166,13 @@
         <v>0</v>
       </c>
       <c r="AJ263">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="264" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK263">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="264" spans="1:37">
       <c r="A264">
         <v>198419</v>
       </c>
@@ -19433,10 +20225,13 @@
         <v>0</v>
       </c>
       <c r="AJ264">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="265" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK264">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="265" spans="1:37">
       <c r="A265">
         <v>198419</v>
       </c>
@@ -19489,10 +20284,13 @@
         <v>0</v>
       </c>
       <c r="AJ265">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="266" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK265">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="266" spans="1:37">
       <c r="A266">
         <v>198464</v>
       </c>
@@ -19584,10 +20382,13 @@
         <v>0</v>
       </c>
       <c r="AJ266">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="267" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK266">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="267" spans="1:37">
       <c r="A267">
         <v>199102</v>
       </c>
@@ -19679,10 +20480,13 @@
         <v>0</v>
       </c>
       <c r="AJ267">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="268" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK267">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="268" spans="1:37">
       <c r="A268">
         <v>199120</v>
       </c>
@@ -19774,10 +20578,13 @@
         <v>1</v>
       </c>
       <c r="AJ268">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="269" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK268">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="269" spans="1:37">
       <c r="A269">
         <v>199120</v>
       </c>
@@ -19869,10 +20676,13 @@
         <v>1</v>
       </c>
       <c r="AJ269">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="270" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK269">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="270" spans="1:37">
       <c r="A270">
         <v>199139</v>
       </c>
@@ -19964,10 +20774,13 @@
         <v>0</v>
       </c>
       <c r="AJ270">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="271" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK270">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="271" spans="1:37">
       <c r="A271">
         <v>199157</v>
       </c>
@@ -20059,10 +20872,13 @@
         <v>0</v>
       </c>
       <c r="AJ271">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="272" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK271">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="272" spans="1:37">
       <c r="A272">
         <v>199193</v>
       </c>
@@ -20154,10 +20970,13 @@
         <v>0</v>
       </c>
       <c r="AJ272">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="273" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK272">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="273" spans="1:37">
       <c r="A273">
         <v>199193</v>
       </c>
@@ -20249,10 +21068,13 @@
         <v>0</v>
       </c>
       <c r="AJ273">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="274" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK273">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="274" spans="1:37">
       <c r="A274">
         <v>199847</v>
       </c>
@@ -20305,10 +21127,13 @@
         <v>0</v>
       </c>
       <c r="AJ274">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="275" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK274">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="275" spans="1:37">
       <c r="A275">
         <v>199847</v>
       </c>
@@ -20361,10 +21186,13 @@
         <v>0</v>
       </c>
       <c r="AJ275">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="276" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK275">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="276" spans="1:37">
       <c r="A276">
         <v>200280</v>
       </c>
@@ -20417,10 +21245,13 @@
         <v>0</v>
       </c>
       <c r="AJ276">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="277" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK276">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="277" spans="1:37">
       <c r="A277">
         <v>200280</v>
       </c>
@@ -20473,10 +21304,13 @@
         <v>0</v>
       </c>
       <c r="AJ277">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="278" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK277">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="278" spans="1:37">
       <c r="A278">
         <v>200332</v>
       </c>
@@ -20568,10 +21402,13 @@
         <v>0</v>
       </c>
       <c r="AJ278">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="279" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK278">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="279" spans="1:37">
       <c r="A279">
         <v>200332</v>
       </c>
@@ -20663,10 +21500,13 @@
         <v>0</v>
       </c>
       <c r="AJ279">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="280" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK279">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="280" spans="1:37">
       <c r="A280">
         <v>200800</v>
       </c>
@@ -20758,10 +21598,13 @@
         <v>1</v>
       </c>
       <c r="AJ280">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="281" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK280">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="281" spans="1:37">
       <c r="A281">
         <v>201441</v>
       </c>
@@ -20814,10 +21657,13 @@
         <v>1</v>
       </c>
       <c r="AJ281">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="282" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK281">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="282" spans="1:37">
       <c r="A282">
         <v>201645</v>
       </c>
@@ -20909,10 +21755,13 @@
         <v>0</v>
       </c>
       <c r="AJ282">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="283" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK282">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="283" spans="1:37">
       <c r="A283">
         <v>201645</v>
       </c>
@@ -21004,10 +21853,13 @@
         <v>1</v>
       </c>
       <c r="AJ283">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="284" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK283">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="284" spans="1:37">
       <c r="A284">
         <v>201885</v>
       </c>
@@ -21099,10 +21951,13 @@
         <v>0</v>
       </c>
       <c r="AJ284">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="285" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK284">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="285" spans="1:37">
       <c r="A285">
         <v>201885</v>
       </c>
@@ -21194,10 +22049,13 @@
         <v>0</v>
       </c>
       <c r="AJ285">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="286" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK285">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="286" spans="1:37">
       <c r="A286">
         <v>202134</v>
       </c>
@@ -21289,10 +22147,13 @@
         <v>1</v>
       </c>
       <c r="AJ286">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="287" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK286">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="287" spans="1:37">
       <c r="A287">
         <v>203368</v>
       </c>
@@ -21345,10 +22206,13 @@
         <v>0</v>
       </c>
       <c r="AJ287">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="288" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK287">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="288" spans="1:37">
       <c r="A288">
         <v>203517</v>
       </c>
@@ -21440,10 +22304,13 @@
         <v>2</v>
       </c>
       <c r="AJ288">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="289" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK288">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="289" spans="1:37">
       <c r="A289">
         <v>203517</v>
       </c>
@@ -21535,10 +22402,13 @@
         <v>1</v>
       </c>
       <c r="AJ289">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="290" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK289">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="290" spans="1:37">
       <c r="A290">
         <v>204024</v>
       </c>
@@ -21630,10 +22500,13 @@
         <v>0</v>
       </c>
       <c r="AJ290">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="291" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK290">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="291" spans="1:37">
       <c r="A291">
         <v>204796</v>
       </c>
@@ -21686,10 +22559,13 @@
         <v>0</v>
       </c>
       <c r="AJ291">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="292" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK291">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="292" spans="1:37">
       <c r="A292">
         <v>204796</v>
       </c>
@@ -21742,10 +22618,13 @@
         <v>4</v>
       </c>
       <c r="AJ292">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="293" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK292">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="293" spans="1:37">
       <c r="A293">
         <v>204857</v>
       </c>
@@ -21837,10 +22716,13 @@
         <v>2</v>
       </c>
       <c r="AJ293">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="294" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK293">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="294" spans="1:37">
       <c r="A294">
         <v>204857</v>
       </c>
@@ -21932,10 +22814,13 @@
         <v>2</v>
       </c>
       <c r="AJ294">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="295" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK294">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="295" spans="1:37">
       <c r="A295">
         <v>206084</v>
       </c>
@@ -22027,10 +22912,13 @@
         <v>0</v>
       </c>
       <c r="AJ295">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="296" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK295">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="296" spans="1:37">
       <c r="A296">
         <v>206084</v>
       </c>
@@ -22122,10 +23010,13 @@
         <v>0</v>
       </c>
       <c r="AJ296">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="297" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK296">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="297" spans="1:37">
       <c r="A297">
         <v>206084</v>
       </c>
@@ -22217,10 +23108,13 @@
         <v>0</v>
       </c>
       <c r="AJ297">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="298" spans="1:36">
+        <v>2</v>
+      </c>
+      <c r="AK297">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="298" spans="1:37">
       <c r="A298">
         <v>206604</v>
       </c>
@@ -22312,10 +23206,13 @@
         <v>0</v>
       </c>
       <c r="AJ298">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="299" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK298">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="299" spans="1:37">
       <c r="A299">
         <v>207388</v>
       </c>
@@ -22422,10 +23319,13 @@
         <v>2</v>
       </c>
       <c r="AJ299">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="300" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK299">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="300" spans="1:37">
       <c r="A300">
         <v>207388</v>
       </c>
@@ -22532,10 +23432,13 @@
         <v>0</v>
       </c>
       <c r="AJ300">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="301" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK300">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="301" spans="1:37">
       <c r="A301">
         <v>207500</v>
       </c>
@@ -22627,10 +23530,13 @@
         <v>1</v>
       </c>
       <c r="AJ301">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="302" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK301">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="302" spans="1:37">
       <c r="A302">
         <v>207500</v>
       </c>
@@ -22722,10 +23628,13 @@
         <v>2</v>
       </c>
       <c r="AJ302">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="303" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK302">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="303" spans="1:37">
       <c r="A303">
         <v>207971</v>
       </c>
@@ -22817,10 +23726,13 @@
         <v>1</v>
       </c>
       <c r="AJ303">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="304" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK303">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="304" spans="1:37">
       <c r="A304">
         <v>209542</v>
       </c>
@@ -22912,10 +23824,13 @@
         <v>0</v>
       </c>
       <c r="AJ304">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="305" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK304">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="305" spans="1:37">
       <c r="A305">
         <v>209551</v>
       </c>
@@ -23007,10 +23922,13 @@
         <v>1</v>
       </c>
       <c r="AJ305">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="306" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK305">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="306" spans="1:37">
       <c r="A306">
         <v>209551</v>
       </c>
@@ -23102,10 +24020,13 @@
         <v>0</v>
       </c>
       <c r="AJ306">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="307" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK306">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="307" spans="1:37">
       <c r="A307">
         <v>209807</v>
       </c>
@@ -23197,10 +24118,13 @@
         <v>2</v>
       </c>
       <c r="AJ307">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="308" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK307">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="308" spans="1:37">
       <c r="A308">
         <v>209807</v>
       </c>
@@ -23292,10 +24216,13 @@
         <v>0</v>
       </c>
       <c r="AJ308">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="309" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK308">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="309" spans="1:37">
       <c r="A309">
         <v>211273</v>
       </c>
@@ -23348,10 +24275,13 @@
         <v>0</v>
       </c>
       <c r="AJ309">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="310" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK309">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="310" spans="1:37">
       <c r="A310">
         <v>211361</v>
       </c>
@@ -23404,10 +24334,13 @@
         <v>0</v>
       </c>
       <c r="AJ310">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="311" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK310">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="311" spans="1:37">
       <c r="A311">
         <v>211440</v>
       </c>
@@ -23499,10 +24432,13 @@
         <v>0</v>
       </c>
       <c r="AJ311">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="312" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK311">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="312" spans="1:37">
       <c r="A312">
         <v>211440</v>
       </c>
@@ -23594,10 +24530,13 @@
         <v>1</v>
       </c>
       <c r="AJ312">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="313" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK312">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="313" spans="1:37">
       <c r="A313">
         <v>213020</v>
       </c>
@@ -23650,10 +24589,13 @@
         <v>1</v>
       </c>
       <c r="AJ313">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="314" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK313">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="314" spans="1:37">
       <c r="A314">
         <v>213543</v>
       </c>
@@ -23706,10 +24648,13 @@
         <v>3</v>
       </c>
       <c r="AJ314">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="315" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK314">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="315" spans="1:37">
       <c r="A315">
         <v>213543</v>
       </c>
@@ -23762,10 +24707,13 @@
         <v>2</v>
       </c>
       <c r="AJ315">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="316" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK315">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="316" spans="1:37">
       <c r="A316">
         <v>214777</v>
       </c>
@@ -23857,10 +24805,13 @@
         <v>0</v>
       </c>
       <c r="AJ316">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="317" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK316">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="317" spans="1:37">
       <c r="A317">
         <v>214777</v>
       </c>
@@ -23952,10 +24903,13 @@
         <v>0</v>
       </c>
       <c r="AJ317">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="318" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK317">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="318" spans="1:37">
       <c r="A318">
         <v>215062</v>
       </c>
@@ -24047,10 +25001,13 @@
         <v>0</v>
       </c>
       <c r="AJ318">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="319" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK318">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="319" spans="1:37">
       <c r="A319">
         <v>215062</v>
       </c>
@@ -24142,10 +25099,13 @@
         <v>1</v>
       </c>
       <c r="AJ319">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="320" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK319">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="320" spans="1:37">
       <c r="A320">
         <v>215293</v>
       </c>
@@ -24237,10 +25197,13 @@
         <v>4</v>
       </c>
       <c r="AJ320">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="321" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK320">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="321" spans="1:37">
       <c r="A321">
         <v>215293</v>
       </c>
@@ -24332,10 +25295,13 @@
         <v>2</v>
       </c>
       <c r="AJ321">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="322" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK321">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="322" spans="1:37">
       <c r="A322">
         <v>216339</v>
       </c>
@@ -24388,10 +25354,13 @@
         <v>0</v>
       </c>
       <c r="AJ322">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="323" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK322">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="323" spans="1:37">
       <c r="A323">
         <v>216339</v>
       </c>
@@ -24444,10 +25413,13 @@
         <v>1</v>
       </c>
       <c r="AJ323">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="324" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK323">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="324" spans="1:37">
       <c r="A324">
         <v>217156</v>
       </c>
@@ -24539,10 +25511,13 @@
         <v>1</v>
       </c>
       <c r="AJ324">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="325" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK324">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="325" spans="1:37">
       <c r="A325">
         <v>217156</v>
       </c>
@@ -24634,10 +25609,13 @@
         <v>3</v>
       </c>
       <c r="AJ325">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="326" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK325">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="326" spans="1:37">
       <c r="A326">
         <v>217484</v>
       </c>
@@ -24690,10 +25668,13 @@
         <v>0</v>
       </c>
       <c r="AJ326">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="327" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK326">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="327" spans="1:37">
       <c r="A327">
         <v>217484</v>
       </c>
@@ -24746,10 +25727,13 @@
         <v>0</v>
       </c>
       <c r="AJ327">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="328" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK327">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="328" spans="1:37">
       <c r="A328">
         <v>217882</v>
       </c>
@@ -24841,10 +25825,13 @@
         <v>0</v>
       </c>
       <c r="AJ328">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="329" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK328">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="329" spans="1:37">
       <c r="A329">
         <v>217882</v>
       </c>
@@ -24936,10 +25923,13 @@
         <v>0</v>
       </c>
       <c r="AJ329">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="330" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK329">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="330" spans="1:37">
       <c r="A330">
         <v>218663</v>
       </c>
@@ -25031,10 +26021,13 @@
         <v>1</v>
       </c>
       <c r="AJ330">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="331" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK330">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="331" spans="1:37">
       <c r="A331">
         <v>218663</v>
       </c>
@@ -25126,10 +26119,13 @@
         <v>1</v>
       </c>
       <c r="AJ331">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="332" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK331">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="332" spans="1:37">
       <c r="A332">
         <v>220181</v>
       </c>
@@ -25221,10 +26217,13 @@
         <v>0</v>
       </c>
       <c r="AJ332">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="333" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK332">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="333" spans="1:37">
       <c r="A333">
         <v>220862</v>
       </c>
@@ -25316,10 +26315,13 @@
         <v>0</v>
       </c>
       <c r="AJ333">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="334" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK333">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="334" spans="1:37">
       <c r="A334">
         <v>221759</v>
       </c>
@@ -25372,10 +26374,13 @@
         <v>1</v>
       </c>
       <c r="AJ334">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="335" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK334">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="335" spans="1:37">
       <c r="A335">
         <v>221759</v>
       </c>
@@ -25428,10 +26433,13 @@
         <v>2</v>
       </c>
       <c r="AJ335">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="336" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK335">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="336" spans="1:37">
       <c r="A336">
         <v>221999</v>
       </c>
@@ -25484,10 +26492,13 @@
         <v>0</v>
       </c>
       <c r="AJ336">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="337" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK336">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="337" spans="1:37">
       <c r="A337">
         <v>221999</v>
       </c>
@@ -25540,10 +26551,13 @@
         <v>0</v>
       </c>
       <c r="AJ337">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="338" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK337">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="338" spans="1:37">
       <c r="A338">
         <v>221999</v>
       </c>
@@ -25596,10 +26610,13 @@
         <v>0</v>
       </c>
       <c r="AJ338">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="339" spans="1:36">
+        <v>2</v>
+      </c>
+      <c r="AK338">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="339" spans="1:37">
       <c r="A339">
         <v>221999</v>
       </c>
@@ -25652,10 +26669,13 @@
         <v>0</v>
       </c>
       <c r="AJ339">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="340" spans="1:36">
+        <v>2</v>
+      </c>
+      <c r="AK339">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="340" spans="1:37">
       <c r="A340">
         <v>223232</v>
       </c>
@@ -25747,10 +26767,13 @@
         <v>0</v>
       </c>
       <c r="AJ340">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="341" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK340">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="341" spans="1:37">
       <c r="A341">
         <v>223232</v>
       </c>
@@ -25842,10 +26865,13 @@
         <v>0</v>
       </c>
       <c r="AJ341">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="342" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK341">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="342" spans="1:37">
       <c r="A342">
         <v>224554</v>
       </c>
@@ -25937,10 +26963,13 @@
         <v>0</v>
       </c>
       <c r="AJ342">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="343" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK342">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="343" spans="1:37">
       <c r="A343">
         <v>225414</v>
       </c>
@@ -25993,10 +27022,13 @@
         <v>0</v>
       </c>
       <c r="AJ343">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="344" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK343">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="344" spans="1:37">
       <c r="A344">
         <v>225511</v>
       </c>
@@ -26088,10 +27120,13 @@
         <v>5</v>
       </c>
       <c r="AJ344">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="345" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK344">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="345" spans="1:37">
       <c r="A345">
         <v>225511</v>
       </c>
@@ -26183,10 +27218,13 @@
         <v>4</v>
       </c>
       <c r="AJ345">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="346" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK345">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="346" spans="1:37">
       <c r="A346">
         <v>227216</v>
       </c>
@@ -26278,10 +27316,13 @@
         <v>0</v>
       </c>
       <c r="AJ346">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="347" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK346">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="347" spans="1:37">
       <c r="A347">
         <v>227216</v>
       </c>
@@ -26373,10 +27414,13 @@
         <v>0</v>
       </c>
       <c r="AJ347">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="348" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK347">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="348" spans="1:37">
       <c r="A348">
         <v>227377</v>
       </c>
@@ -26429,10 +27473,13 @@
         <v>0</v>
       </c>
       <c r="AJ348">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="349" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK348">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="349" spans="1:37">
       <c r="A349">
         <v>227757</v>
       </c>
@@ -26485,10 +27532,13 @@
         <v>2</v>
       </c>
       <c r="AJ349">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="350" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK349">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="350" spans="1:37">
       <c r="A350">
         <v>227757</v>
       </c>
@@ -26541,10 +27591,13 @@
         <v>0</v>
       </c>
       <c r="AJ350">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="351" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK350">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="351" spans="1:37">
       <c r="A351">
         <v>228246</v>
       </c>
@@ -26597,10 +27650,13 @@
         <v>0</v>
       </c>
       <c r="AJ351">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="352" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK351">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="352" spans="1:37">
       <c r="A352">
         <v>228246</v>
       </c>
@@ -26653,10 +27709,13 @@
         <v>1</v>
       </c>
       <c r="AJ352">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="353" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK352">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="353" spans="1:37">
       <c r="A353">
         <v>228431</v>
       </c>
@@ -26709,10 +27768,13 @@
         <v>0</v>
       </c>
       <c r="AJ353">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="354" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK353">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="354" spans="1:37">
       <c r="A354">
         <v>228459</v>
       </c>
@@ -26765,10 +27827,13 @@
         <v>0</v>
       </c>
       <c r="AJ354">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="355" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK354">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="355" spans="1:37">
       <c r="A355">
         <v>228723</v>
       </c>
@@ -26860,10 +27925,13 @@
         <v>1</v>
       </c>
       <c r="AJ355">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="356" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK355">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="356" spans="1:37">
       <c r="A356">
         <v>228723</v>
       </c>
@@ -26955,10 +28023,13 @@
         <v>1</v>
       </c>
       <c r="AJ356">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="357" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK356">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="357" spans="1:37">
       <c r="A357">
         <v>228769</v>
       </c>
@@ -27050,10 +28121,13 @@
         <v>0</v>
       </c>
       <c r="AJ357">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="358" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK357">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="358" spans="1:37">
       <c r="A358">
         <v>228769</v>
       </c>
@@ -27145,10 +28219,13 @@
         <v>1</v>
       </c>
       <c r="AJ358">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="359" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK358">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="359" spans="1:37">
       <c r="A359">
         <v>228778</v>
       </c>
@@ -27201,10 +28278,13 @@
         <v>1</v>
       </c>
       <c r="AJ359">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="360" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK359">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="360" spans="1:37">
       <c r="A360">
         <v>228778</v>
       </c>
@@ -27257,10 +28337,13 @@
         <v>0</v>
       </c>
       <c r="AJ360">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="361" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK360">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="361" spans="1:37">
       <c r="A361">
         <v>228787</v>
       </c>
@@ -27352,10 +28435,13 @@
         <v>0</v>
       </c>
       <c r="AJ361">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="362" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK361">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="362" spans="1:37">
       <c r="A362">
         <v>228787</v>
       </c>
@@ -27447,10 +28533,13 @@
         <v>2</v>
       </c>
       <c r="AJ362">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="363" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK362">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="363" spans="1:37">
       <c r="A363">
         <v>228796</v>
       </c>
@@ -27542,10 +28631,13 @@
         <v>0</v>
       </c>
       <c r="AJ363">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="364" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK363">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="364" spans="1:37">
       <c r="A364">
         <v>228875</v>
       </c>
@@ -27637,10 +28729,13 @@
         <v>1</v>
       </c>
       <c r="AJ364">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="365" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK364">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="365" spans="1:37">
       <c r="A365">
         <v>229027</v>
       </c>
@@ -27693,10 +28788,13 @@
         <v>0</v>
       </c>
       <c r="AJ365">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="366" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK365">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="366" spans="1:37">
       <c r="A366">
         <v>229027</v>
       </c>
@@ -27749,10 +28847,13 @@
         <v>0</v>
       </c>
       <c r="AJ366">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="367" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK366">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="367" spans="1:37">
       <c r="A367">
         <v>229115</v>
       </c>
@@ -27805,10 +28906,13 @@
         <v>1</v>
       </c>
       <c r="AJ367">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="368" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK367">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="368" spans="1:37">
       <c r="A368">
         <v>229115</v>
       </c>
@@ -27861,10 +28965,13 @@
         <v>0</v>
       </c>
       <c r="AJ368">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="369" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK368">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="369" spans="1:37">
       <c r="A369">
         <v>230038</v>
       </c>
@@ -27956,10 +29063,13 @@
         <v>0</v>
       </c>
       <c r="AJ369">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="370" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK369">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="370" spans="1:37">
       <c r="A370">
         <v>230038</v>
       </c>
@@ -28051,10 +29161,13 @@
         <v>0</v>
       </c>
       <c r="AJ370">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="371" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK370">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="371" spans="1:37">
       <c r="A371">
         <v>230728</v>
       </c>
@@ -28107,10 +29220,13 @@
         <v>0</v>
       </c>
       <c r="AJ371">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="372" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK371">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="372" spans="1:37">
       <c r="A372">
         <v>230728</v>
       </c>
@@ -28163,10 +29279,13 @@
         <v>1</v>
       </c>
       <c r="AJ372">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="373" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK372">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="373" spans="1:37">
       <c r="A373">
         <v>230764</v>
       </c>
@@ -28258,10 +29377,13 @@
         <v>0</v>
       </c>
       <c r="AJ373">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="374" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK373">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="374" spans="1:37">
       <c r="A374">
         <v>230764</v>
       </c>
@@ -28353,10 +29475,13 @@
         <v>1</v>
       </c>
       <c r="AJ374">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="375" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK374">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="375" spans="1:37">
       <c r="A375">
         <v>231174</v>
       </c>
@@ -28409,10 +29534,13 @@
         <v>0</v>
       </c>
       <c r="AJ375">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="376" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK375">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="376" spans="1:37">
       <c r="A376">
         <v>231624</v>
       </c>
@@ -28504,10 +29632,13 @@
         <v>3</v>
       </c>
       <c r="AJ376">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="377" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK376">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="377" spans="1:37">
       <c r="A377">
         <v>231624</v>
       </c>
@@ -28599,10 +29730,13 @@
         <v>0</v>
       </c>
       <c r="AJ377">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="378" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK377">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="378" spans="1:37">
       <c r="A378">
         <v>232186</v>
       </c>
@@ -28655,10 +29789,13 @@
         <v>0</v>
       </c>
       <c r="AJ378">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="379" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK378">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="379" spans="1:37">
       <c r="A379">
         <v>232265</v>
       </c>
@@ -28711,10 +29848,13 @@
         <v>0</v>
       </c>
       <c r="AJ379">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="380" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK379">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="380" spans="1:37">
       <c r="A380">
         <v>232265</v>
       </c>
@@ -28767,10 +29907,13 @@
         <v>0</v>
       </c>
       <c r="AJ380">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="381" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK380">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="381" spans="1:37">
       <c r="A381">
         <v>232982</v>
       </c>
@@ -28823,10 +29966,13 @@
         <v>0</v>
       </c>
       <c r="AJ381">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="382" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK381">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="382" spans="1:37">
       <c r="A382">
         <v>232982</v>
       </c>
@@ -28879,10 +30025,13 @@
         <v>1</v>
       </c>
       <c r="AJ382">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="383" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK382">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="383" spans="1:37">
       <c r="A383">
         <v>233921</v>
       </c>
@@ -28935,10 +30084,13 @@
         <v>1</v>
       </c>
       <c r="AJ383">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="384" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK383">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="384" spans="1:37">
       <c r="A384">
         <v>233921</v>
       </c>
@@ -28991,10 +30143,13 @@
         <v>0</v>
       </c>
       <c r="AJ384">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="385" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK384">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="385" spans="1:37">
       <c r="A385">
         <v>234030</v>
       </c>
@@ -29047,10 +30202,13 @@
         <v>1</v>
       </c>
       <c r="AJ385">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="386" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK385">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="386" spans="1:37">
       <c r="A386">
         <v>234076</v>
       </c>
@@ -29103,10 +30261,13 @@
         <v>2</v>
       </c>
       <c r="AJ386">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="387" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK386">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="387" spans="1:37">
       <c r="A387">
         <v>234076</v>
       </c>
@@ -29159,10 +30320,13 @@
         <v>1</v>
       </c>
       <c r="AJ387">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="388" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK387">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="388" spans="1:37">
       <c r="A388">
         <v>234155</v>
       </c>
@@ -29215,10 +30379,13 @@
         <v>0</v>
       </c>
       <c r="AJ388">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="389" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK388">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="389" spans="1:37">
       <c r="A389">
         <v>236939</v>
       </c>
@@ -29310,10 +30477,13 @@
         <v>0</v>
       </c>
       <c r="AJ389">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="390" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK389">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="390" spans="1:37">
       <c r="A390">
         <v>236939</v>
       </c>
@@ -29405,10 +30575,13 @@
         <v>1</v>
       </c>
       <c r="AJ390">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="391" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK390">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="391" spans="1:37">
       <c r="A391">
         <v>236948</v>
       </c>
@@ -29461,10 +30634,13 @@
         <v>1</v>
       </c>
       <c r="AJ391">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="392" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK391">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="392" spans="1:37">
       <c r="A392">
         <v>236948</v>
       </c>
@@ -29517,10 +30693,13 @@
         <v>0</v>
       </c>
       <c r="AJ392">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="393" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK392">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="393" spans="1:37">
       <c r="A393">
         <v>238032</v>
       </c>
@@ -29612,10 +30791,13 @@
         <v>0</v>
       </c>
       <c r="AJ393">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="394" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK393">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="394" spans="1:37">
       <c r="A394">
         <v>238032</v>
       </c>
@@ -29707,10 +30889,13 @@
         <v>0</v>
       </c>
       <c r="AJ394">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="395" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK394">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="395" spans="1:37">
       <c r="A395">
         <v>240444</v>
       </c>
@@ -29802,10 +30987,13 @@
         <v>2</v>
       </c>
       <c r="AJ395">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="396" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK395">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="396" spans="1:37">
       <c r="A396">
         <v>240444</v>
       </c>
@@ -29897,10 +31085,13 @@
         <v>1</v>
       </c>
       <c r="AJ396">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="397" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK396">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="397" spans="1:37">
       <c r="A397">
         <v>240453</v>
       </c>
@@ -29992,10 +31183,13 @@
         <v>1</v>
       </c>
       <c r="AJ397">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="398" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK397">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="398" spans="1:37">
       <c r="A398">
         <v>240453</v>
       </c>
@@ -30087,10 +31281,13 @@
         <v>0</v>
       </c>
       <c r="AJ398">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="399" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK398">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="399" spans="1:37">
       <c r="A399">
         <v>240727</v>
       </c>
@@ -30182,10 +31379,13 @@
         <v>0</v>
       </c>
       <c r="AJ399">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="400" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK399">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="400" spans="1:37">
       <c r="A400">
         <v>240727</v>
       </c>
@@ -30277,10 +31477,13 @@
         <v>0</v>
       </c>
       <c r="AJ400">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="401" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK400">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="401" spans="1:37">
       <c r="A401">
         <v>243197</v>
       </c>
@@ -30372,10 +31575,13 @@
         <v>3</v>
       </c>
       <c r="AJ401">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="402" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK401">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="402" spans="1:37">
       <c r="A402">
         <v>243221</v>
       </c>
@@ -30467,10 +31673,13 @@
         <v>0</v>
       </c>
       <c r="AJ402">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="403" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK402">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="403" spans="1:37">
       <c r="A403">
         <v>243744</v>
       </c>
@@ -30523,10 +31732,13 @@
         <v>1</v>
       </c>
       <c r="AJ403">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="404" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK403">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="404" spans="1:37">
       <c r="A404">
         <v>243744</v>
       </c>
@@ -30579,10 +31791,13 @@
         <v>3</v>
       </c>
       <c r="AJ404">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="405" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK404">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="405" spans="1:37">
       <c r="A405">
         <v>243780</v>
       </c>
@@ -30635,10 +31850,13 @@
         <v>1</v>
       </c>
       <c r="AJ405">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="406" spans="1:36">
+        <v>1</v>
+      </c>
+      <c r="AK405">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="406" spans="1:37">
       <c r="A406">
         <v>243780</v>
       </c>
@@ -30691,6 +31909,9 @@
         <v>0</v>
       </c>
       <c r="AJ406">
+        <v>1</v>
+      </c>
+      <c r="AK406">
         <v>2010</v>
       </c>
     </row>
